--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-management-v2\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96dbc1fdb7cb27ef/Desktop/Substitute-management-v2/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7476130-D5B2-4787-BEA3-F4A20E122C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{F7476130-D5B2-4787-BEA3-F4A20E122C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0919C61-D213-4103-B683-1DD5B778FC70}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="138">
   <si>
     <t>Teacher</t>
   </si>
@@ -66,12 +66,6 @@
     <t>11 ARTS F</t>
   </si>
   <si>
-    <t>10th A</t>
-  </si>
-  <si>
-    <t>12ARTS B</t>
-  </si>
-  <si>
     <t>10TH  A</t>
   </si>
   <si>
@@ -96,9 +90,6 @@
     <t>9TH F</t>
   </si>
   <si>
-    <t>11 ARTS</t>
-  </si>
-  <si>
     <t xml:space="preserve">9TH </t>
   </si>
   <si>
@@ -171,9 +162,6 @@
     <t>SH.RUPESH</t>
   </si>
   <si>
-    <t>SH.INDER</t>
-  </si>
-  <si>
     <t>SH.BIJENDER KUMAR</t>
   </si>
   <si>
@@ -327,9 +315,6 @@
     <t>11TH SCI B(1-2)</t>
   </si>
   <si>
-    <t>11TH SCI B(5-6)</t>
-  </si>
-  <si>
     <t>11TH SCI C</t>
   </si>
   <si>
@@ -402,7 +387,64 @@
     <t>SH.NAVEEN KUMAR</t>
   </si>
   <si>
-    <t>11TH SCI A(3-4)                11SCI D(5-6)</t>
+    <t>10TH B</t>
+  </si>
+  <si>
+    <t>11 TH ARTS A</t>
+  </si>
+  <si>
+    <t>11TH ARTS A+B</t>
+  </si>
+  <si>
+    <t>12TH ARTS B+E</t>
+  </si>
+  <si>
+    <t>11TH ARTS C+A</t>
+  </si>
+  <si>
+    <t>12 SCI A</t>
+  </si>
+  <si>
+    <t>11TH SCI B(3-4)                11SCI D(5-6)</t>
+  </si>
+  <si>
+    <t>11TH SCI A(5-6)</t>
+  </si>
+  <si>
+    <t>11 SCI C(5,6)</t>
+  </si>
+  <si>
+    <t>12 SCI C(1,2)</t>
+  </si>
+  <si>
+    <t>11 SCI A(1,2)</t>
+  </si>
+  <si>
+    <t>12 SCI B(3,4)</t>
+  </si>
+  <si>
+    <t>11TH SCI B(5,6)</t>
+  </si>
+  <si>
+    <t>12TH SCI A(3,4)</t>
+  </si>
+  <si>
+    <t>11TH SCI C(1,2)</t>
+  </si>
+  <si>
+    <t>12TH SCI B(5,6)</t>
+  </si>
+  <si>
+    <t>11TH ARTS</t>
+  </si>
+  <si>
+    <t>11TH ARTS F</t>
+  </si>
+  <si>
+    <t>11TH ARTS A(3,4)</t>
+  </si>
+  <si>
+    <t>12TH SCI A(5,6)</t>
   </si>
 </sst>
 </file>
@@ -486,7 +528,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -514,7 +556,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -821,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
@@ -858,1022 +900,1056 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="A2" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>121</v>
+      <c r="E2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>87</v>
+        <v>23</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>121</v>
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>95</v>
+        <v>102</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>94</v>
+        <v>25</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>103</v>
+        <v>85</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>88</v>
+        <v>26</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>102</v>
+        <v>27</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>121</v>
+        <v>109</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>118</v>
+      <c r="C8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>112</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>121</v>
+        <v>15</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>100</v>
+        <v>116</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>12</v>
+        <v>30</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>102</v>
+        <v>32</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>17</v>
+        <v>100</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>110</v>
+        <v>116</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>18</v>
+        <v>97</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>107</v>
+        <v>116</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>118</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>20</v>
+        <v>116</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>93</v>
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G14" s="1"/>
+        <v>116</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>13</v>
+        <v>116</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>84</v>
+        <v>119</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>9</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="8" t="s">
-        <v>7</v>
+        <v>116</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>121</v>
+        <v>109</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="D18" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="C19" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>98</v>
+      </c>
       <c r="E20" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>111</v>
+        <v>15</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>121</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>86</v>
+      <c r="E22" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>122</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="D23" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C32" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="D32" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>7</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="C37" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" s="3"/>
+        <v>82</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="D38" s="1" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D39" s="7"/>
+        <v>81</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>94</v>
+      </c>
       <c r="E39" s="1" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E40" s="3"/>
+        <v>84</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="F40" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D41" s="9"/>
+        <v>111</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>92</v>
+      </c>
       <c r="E41" s="1" t="s">
         <v>116</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D42" s="1"/>
+      <c r="D42" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="E42" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G42" s="7"/>
+        <v>132</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E43" s="6"/>
+        <v>110</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="F43" s="1" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E44" s="6"/>
+        <v>110</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="F44" s="1" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>8</v>
@@ -1881,301 +1957,278 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="F57" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="G57" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96dbc1fdb7cb27ef/Desktop/Substitute-management-v2/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{F7476130-D5B2-4787-BEA3-F4A20E122C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0919C61-D213-4103-B683-1DD5B778FC70}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{F7476130-D5B2-4787-BEA3-F4A20E122C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDFAA598-8696-448E-964D-48DA04CD2356}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1857,7 +1857,7 @@
         <v>134</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>20</v>
@@ -1880,7 +1880,7 @@
         <v>134</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>20</v>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96dbc1fdb7cb27ef/Desktop/Substitute-management-v2/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{F7476130-D5B2-4787-BEA3-F4A20E122C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDFAA598-8696-448E-964D-48DA04CD2356}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0832F67-B75F-41B0-B637-9139A06FA3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="136">
   <si>
     <t>Teacher</t>
   </si>
@@ -63,18 +63,12 @@
     <t>9TH C</t>
   </si>
   <si>
-    <t>11 ARTS F</t>
-  </si>
-  <si>
     <t>10TH  A</t>
   </si>
   <si>
     <t xml:space="preserve">11 SCI </t>
   </si>
   <si>
-    <t>12 SCI</t>
-  </si>
-  <si>
     <t>10TH A</t>
   </si>
   <si>
@@ -258,9 +252,6 @@
     <t>SMT.NANCY</t>
   </si>
   <si>
-    <t>SMT.Usha (PTI)</t>
-  </si>
-  <si>
     <t>SH.JITENDER BAJAJ</t>
   </si>
   <si>
@@ -321,9 +312,6 @@
     <t>11TH SCI D</t>
   </si>
   <si>
-    <t>11TH SCI D(3-4)</t>
-  </si>
-  <si>
     <t>11TH COMM A</t>
   </si>
   <si>
@@ -369,18 +357,9 @@
     <t>12TH SCI A</t>
   </si>
   <si>
-    <t>12TH SCI A(1-2)</t>
-  </si>
-  <si>
     <t>12TH SCI B</t>
   </si>
   <si>
-    <t>12TH SCI B (1-2)</t>
-  </si>
-  <si>
-    <t>12TH SCI C(3-4)</t>
-  </si>
-  <si>
     <t>FREE</t>
   </si>
   <si>
@@ -390,9 +369,6 @@
     <t>10TH B</t>
   </si>
   <si>
-    <t>11 TH ARTS A</t>
-  </si>
-  <si>
     <t>11TH ARTS A+B</t>
   </si>
   <si>
@@ -405,24 +381,6 @@
     <t>12 SCI A</t>
   </si>
   <si>
-    <t>11TH SCI B(3-4)                11SCI D(5-6)</t>
-  </si>
-  <si>
-    <t>11TH SCI A(5-6)</t>
-  </si>
-  <si>
-    <t>11 SCI C(5,6)</t>
-  </si>
-  <si>
-    <t>12 SCI C(1,2)</t>
-  </si>
-  <si>
-    <t>11 SCI A(1,2)</t>
-  </si>
-  <si>
-    <t>12 SCI B(3,4)</t>
-  </si>
-  <si>
     <t>11TH SCI B(5,6)</t>
   </si>
   <si>
@@ -445,13 +403,49 @@
   </si>
   <si>
     <t>12TH SCI A(5,6)</t>
+  </si>
+  <si>
+    <t>12TH SCI</t>
+  </si>
+  <si>
+    <t>11TH SCI C(5,6)</t>
+  </si>
+  <si>
+    <t>12TH SCI C(1,2)</t>
+  </si>
+  <si>
+    <t>11TH SCI A(1,2)</t>
+  </si>
+  <si>
+    <t>12TH SCI B(3,4)</t>
+  </si>
+  <si>
+    <t>11TH SCI D(3,4)</t>
+  </si>
+  <si>
+    <t>11TH SCI A(5,6)</t>
+  </si>
+  <si>
+    <t>11TH SCI B(3,4)                11SCI D(5,6)</t>
+  </si>
+  <si>
+    <t>12TH SCI B (1,2)</t>
+  </si>
+  <si>
+    <t>12TH SCI A(1,2)</t>
+  </si>
+  <si>
+    <t>12TH SCI C(3,4)</t>
+  </si>
+  <si>
+    <t>SMT.Usha</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -483,6 +477,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -520,7 +520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -557,6 +557,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -901,342 +904,344 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>105</v>
+        <v>13</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>18</v>
+        <v>109</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F16" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>9</v>
@@ -1244,22 +1249,22 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>7</v>
@@ -1267,689 +1272,689 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="G27" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>7</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C36" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>18</v>
+        <v>92</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F39" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G40" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>92</v>
+        <v>107</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F41" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="F41" s="7" t="s">
-        <v>130</v>
-      </c>
       <c r="G41" s="1" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>8</v>
@@ -1957,278 +1962,278 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="F56" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="G56" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0832F67-B75F-41B0-B637-9139A06FA3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813B3973-6DF0-44D9-851D-084E3CCBB161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,15 +237,6 @@
     <t>SH.SOURABH</t>
   </si>
   <si>
-    <t>SH.Hero Singh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMT.Nisha </t>
-  </si>
-  <si>
-    <t>SMT.Renu</t>
-  </si>
-  <si>
     <t>SH.RAVINDER</t>
   </si>
   <si>
@@ -438,7 +429,16 @@
     <t>12TH SCI C(3,4)</t>
   </si>
   <si>
-    <t>SMT.Usha</t>
+    <t>SMT.USHA</t>
+  </si>
+  <si>
+    <t>SH.HERO SINGH</t>
+  </si>
+  <si>
+    <t>SMT.NISHA</t>
+  </si>
+  <si>
+    <t>SMT.RENU</t>
   </si>
 </sst>
 </file>
@@ -904,25 +904,25 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -930,22 +930,22 @@
         <v>21</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -953,22 +953,22 @@
         <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -976,22 +976,22 @@
         <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -999,22 +999,22 @@
         <v>24</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1022,22 +1022,22 @@
         <v>25</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1045,22 +1045,22 @@
         <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1068,22 +1068,22 @@
         <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1091,22 +1091,22 @@
         <v>28</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>12</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1114,22 +1114,22 @@
         <v>30</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1137,19 +1137,19 @@
         <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>13</v>
@@ -1160,19 +1160,19 @@
         <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>14</v>
@@ -1183,19 +1183,19 @@
         <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>16</v>
@@ -1206,22 +1206,22 @@
         <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1229,10 +1229,10 @@
         <v>34</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>10</v>
@@ -1241,7 +1241,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>9</v>
@@ -1252,19 +1252,19 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>7</v>
@@ -1275,22 +1275,22 @@
         <v>36</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1298,22 +1298,22 @@
         <v>37</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -1324,19 +1324,19 @@
         <v>16</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1344,22 +1344,22 @@
         <v>39</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1367,22 +1367,22 @@
         <v>40</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1393,19 +1393,19 @@
         <v>12</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1413,22 +1413,22 @@
         <v>42</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1439,19 +1439,19 @@
         <v>15</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1462,19 +1462,19 @@
         <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1482,22 +1482,22 @@
         <v>45</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="G27" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1508,19 +1508,19 @@
         <v>14</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1528,22 +1528,22 @@
         <v>47</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1551,22 +1551,22 @@
         <v>48</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1580,16 +1580,16 @@
         <v>16</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -1597,13 +1597,13 @@
         <v>50</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>7</v>
@@ -1612,7 +1612,7 @@
         <v>15</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1620,22 +1620,22 @@
         <v>51</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -1643,7 +1643,7 @@
         <v>52</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>12</v>
@@ -1652,13 +1652,13 @@
         <v>14</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1666,7 +1666,7 @@
         <v>53</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>15</v>
@@ -1675,13 +1675,13 @@
         <v>9</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -1689,22 +1689,22 @@
         <v>54</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C36" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -1712,22 +1712,22 @@
         <v>55</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -1735,22 +1735,22 @@
         <v>56</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1761,19 +1761,19 @@
         <v>13</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -1781,22 +1781,22 @@
         <v>58</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -1807,19 +1807,19 @@
         <v>8</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1827,22 +1827,22 @@
         <v>60</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -1850,16 +1850,16 @@
         <v>61</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>17</v>
@@ -1870,19 +1870,19 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>17</v>
@@ -1896,10 +1896,10 @@
         <v>62</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D45" s="12" t="s">
         <v>19</v>
@@ -1916,13 +1916,13 @@
     </row>
     <row r="46" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D46" s="12" t="s">
         <v>19</v>
@@ -1942,19 +1942,19 @@
         <v>63</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>8</v>
@@ -1965,22 +1965,22 @@
         <v>64</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -1988,10 +1988,10 @@
         <v>65</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>19</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="50" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>19</v>
@@ -2034,10 +2034,10 @@
         <v>66</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>19</v>
@@ -2046,33 +2046,33 @@
         <v>20</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -2080,160 +2080,160 @@
         <v>67</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813B3973-6DF0-44D9-851D-084E3CCBB161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0BCF74-A2B3-4BEC-9844-D49CAD00CD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1399,7 +1399,7 @@
         <v>74</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>79</v>
@@ -1422,7 +1422,7 @@
         <v>99</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>83</v>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaigo\OneDrive\Desktop\Substitute-management-v2\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FF74E7-6D78-40C8-A7D3-99A37D3A046B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BC0B54-7F98-4F06-BCB0-F1BEF8A8B5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timetable" sheetId="1" r:id="rId1"/>
@@ -862,19 +862,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G57"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.796875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.53125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.1328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.86328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.46484375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="32.265625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="23.46484375" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.44140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="34.21875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="23.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -897,7 +897,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
@@ -920,7 +920,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -943,7 +943,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>23</v>
       </c>
@@ -966,7 +966,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>24</v>
       </c>
@@ -989,7 +989,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>25</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>26</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>27</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
@@ -1068,20 +1068,20 @@
       <c r="C9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>90</v>
+      <c r="D9" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>28</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>30</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>31</v>
       </c>
@@ -1150,7 +1150,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>32</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>33</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>34</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>35</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>36</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="20.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>38</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>39</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>42</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>43</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>44</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>45</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>46</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>47</v>
       </c>
@@ -1505,20 +1505,20 @@
       <c r="C28" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>104</v>
+      <c r="D28" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>48</v>
       </c>
@@ -1528,20 +1528,20 @@
       <c r="C29" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>103</v>
+      <c r="D29" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>90</v>
+      <c r="F29" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>49</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>50</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>51</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>52</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="34.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>53</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>54</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>55</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>56</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>57</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>58</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>59</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>60</v>
       </c>
@@ -1811,13 +1811,13 @@
         <v>113</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>72</v>
       </c>
@@ -1834,13 +1834,13 @@
         <v>113</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>61</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>70</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>62</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>63</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>64</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>71</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>65</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>69</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>66</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>128</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>129</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>130</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>131</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>67</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>68</v>
       </c>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BC0B54-7F98-4F06-BCB0-F1BEF8A8B5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3867182E-1191-4AD3-AB61-1319186FEB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1212" yWindow="5664" windowWidth="21336" windowHeight="6708" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timetable" sheetId="1" r:id="rId1"/>
@@ -1069,10 +1069,10 @@
         <v>13</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>90</v>
@@ -1203,8 +1203,8 @@
       <c r="B15" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>99</v>
+      <c r="C15" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>117</v>
@@ -1212,8 +1212,8 @@
       <c r="E15" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>103</v>
+      <c r="F15" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>7</v>
@@ -1388,16 +1388,16 @@
         <v>15</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>133</v>
@@ -1505,14 +1505,14 @@
       <c r="C28" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>103</v>
+      <c r="D28" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>104</v>
+      <c r="F28" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>103</v>
@@ -1689,11 +1689,11 @@
       <c r="C36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>122</v>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-management-v2\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaigo\OneDrive\Desktop\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3867182E-1191-4AD3-AB61-1319186FEB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73157C60-7C44-4C30-8D3E-7D3F25C4734A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1212" yWindow="5664" windowWidth="21336" windowHeight="6708" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timetable" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="155">
   <si>
     <t>Teacher</t>
   </si>
@@ -84,9 +84,6 @@
     <t>9TH F</t>
   </si>
   <si>
-    <t xml:space="preserve">9TH </t>
-  </si>
-  <si>
     <t>10TH</t>
   </si>
   <si>
@@ -439,6 +436,66 @@
   </si>
   <si>
     <t>11TH ARTS F+B</t>
+  </si>
+  <si>
+    <t>12TH ARTS E (SKT)</t>
+  </si>
+  <si>
+    <t>11TH ARTS (SKT)</t>
+  </si>
+  <si>
+    <t>10TH (SKT)</t>
+  </si>
+  <si>
+    <t>11TH ARTS B (CS)</t>
+  </si>
+  <si>
+    <t>12  ARTS+COMM+SCI (CS)</t>
+  </si>
+  <si>
+    <t>11  ARTS+COMM+SCI (CS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9TH (CS) </t>
+  </si>
+  <si>
+    <t>10TH (CS)</t>
+  </si>
+  <si>
+    <t>9TH (P)</t>
+  </si>
+  <si>
+    <t>10TH (P)</t>
+  </si>
+  <si>
+    <t>12 ARTS+COMM+SCI (P)</t>
+  </si>
+  <si>
+    <t>11 ARTS+COMM+SCI (P)</t>
+  </si>
+  <si>
+    <t>12  ARTS+COMM+SCI (IT)</t>
+  </si>
+  <si>
+    <t>11  ARTS+COMM+SCI (IT)</t>
+  </si>
+  <si>
+    <t>9TH (IT)</t>
+  </si>
+  <si>
+    <t>10TH (IT)</t>
+  </si>
+  <si>
+    <t>9TH (PAT)</t>
+  </si>
+  <si>
+    <t>10TH (PAT)</t>
+  </si>
+  <si>
+    <t>11 ARTS+COMM+SCI (PAT)</t>
+  </si>
+  <si>
+    <t>12 ARTS+COMM+SCI (PAT)</t>
   </si>
 </sst>
 </file>
@@ -485,12 +542,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -520,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -559,6 +622,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -862,19 +926,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G57"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.44140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="34.21875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.53125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24.19921875" style="2" customWidth="1"/>
+    <col min="5" max="6" width="24.46484375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="34.19921875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="23.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -897,61 +960,61 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
@@ -960,110 +1023,110 @@
         <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="B6" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>13</v>
@@ -1072,116 +1135,116 @@
         <v>16</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="D11" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>10</v>
@@ -1190,268 +1253,268 @@
         <v>11</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="7" t="s">
+      <c r="B17" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="C17" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="B20" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="G20" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="G23" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>14</v>
@@ -1460,67 +1523,67 @@
         <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F27" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>9</v>
@@ -1529,30 +1592,30 @@
         <v>16</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>7</v>
@@ -1561,38 +1624,38 @@
         <v>15</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>12</v>
@@ -1601,21 +1664,21 @@
         <v>14</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>15</v>
@@ -1624,565 +1687,565 @@
         <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="34.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A35" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A36" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="C36" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G37" s="1" t="s">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
+      <c r="G38" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F39" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G40" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="G40" s="7" t="s">
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A41" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+      <c r="F41" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A42" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
+      <c r="B43" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C43" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D43" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="C45" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
+      <c r="B47" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D47" s="12" t="s">
+      <c r="B49" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E47" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
+      <c r="F49" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A51" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
+      <c r="B51" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A52" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A53" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A54" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A55" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A56" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
+      <c r="B56" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A57" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
-        <v>68</v>
-      </c>
       <c r="B57" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5633FE-DB28-454B-98F4-5BF51B51FA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210307A1-41EB-4E79-BBA3-59FE9426F57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4596" yWindow="192" windowWidth="17472" windowHeight="6708" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timetable" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="157">
   <si>
     <t>Teacher</t>
   </si>
@@ -87,12 +87,6 @@
     <t>10TH</t>
   </si>
   <si>
-    <t>12  ARTS+COMM+SCI</t>
-  </si>
-  <si>
-    <t>11  ARTS+COMM+SCI</t>
-  </si>
-  <si>
     <t>SMT. SAWRAJ</t>
   </si>
   <si>
@@ -496,6 +490,18 @@
   </si>
   <si>
     <t>11TH COMM A +ARTS A</t>
+  </si>
+  <si>
+    <t>11TH ARTS A+B(Geo)</t>
+  </si>
+  <si>
+    <t>12TH ARTS C(Maths)</t>
+  </si>
+  <si>
+    <t>12  ARTS+COMM+SCI(Phy Edu)</t>
+  </si>
+  <si>
+    <t>11  ARTS+COMM+SCI(Phy Edu)</t>
   </si>
 </sst>
 </file>
@@ -931,8 +937,9 @@
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="19.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="24.21875" style="2" customWidth="1"/>
-    <col min="5" max="6" width="24.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.44140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="34.21875" style="2" customWidth="1"/>
     <col min="8" max="8" width="23.44140625" customWidth="1"/>
   </cols>
@@ -962,171 +969,171 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>13</v>
@@ -1135,33 +1142,33 @@
         <v>16</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>8</v>
@@ -1169,22 +1176,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>13</v>
@@ -1192,22 +1199,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>14</v>
@@ -1215,22 +1222,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>16</v>
@@ -1238,36 +1245,36 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>10</v>
@@ -1276,7 +1283,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>9</v>
@@ -1284,22 +1291,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>7</v>
@@ -1307,237 +1314,237 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>14</v>
@@ -1546,67 +1553,67 @@
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>9</v>
@@ -1615,30 +1622,30 @@
         <v>16</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>7</v>
@@ -1647,38 +1654,38 @@
         <v>15</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>12</v>
@@ -1687,217 +1694,217 @@
         <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F35" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G35" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>17</v>
@@ -1905,375 +1912,375 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="F44" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="G44" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D48" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E48" s="12" t="s">
+      <c r="G48" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="F54" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>90</v>
-      </c>
       <c r="G54" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210307A1-41EB-4E79-BBA3-59FE9426F57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2EB3C6-F038-4EF7-89FC-6DC519A1B2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -936,7 +936,7 @@
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" style="2" customWidth="1"/>
     <col min="4" max="4" width="27.109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.77734375" style="2" customWidth="1"/>
     <col min="6" max="6" width="24.44140625" style="2" customWidth="1"/>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2EB3C6-F038-4EF7-89FC-6DC519A1B2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A218DC-EC0C-4081-9784-8A4D8FC4DD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3540" yWindow="0" windowWidth="18600" windowHeight="6708" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timetable" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="156">
   <si>
     <t>Teacher</t>
   </si>
@@ -480,12 +480,6 @@
     <t>12 ARTS+COMM+SCI (PAT)</t>
   </si>
   <si>
-    <t>SH. ANOOP SINGH</t>
-  </si>
-  <si>
-    <t>12 ARTS F</t>
-  </si>
-  <si>
     <t>SH.SHARWAN</t>
   </si>
   <si>
@@ -502,6 +496,9 @@
   </si>
   <si>
     <t>11  ARTS+COMM+SCI(Phy Edu)</t>
+  </si>
+  <si>
+    <t>12TH ARTS D+F</t>
   </si>
 </sst>
 </file>
@@ -931,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
@@ -1004,7 +1001,7 @@
         <v>73</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>99</v>
@@ -1024,7 +1021,7 @@
         <v>87</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
@@ -1050,7 +1047,7 @@
         <v>109</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>97</v>
@@ -1113,7 +1110,7 @@
         <v>93</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>75</v>
@@ -1153,390 +1150,390 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>150</v>
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>8</v>
+      <c r="G10" s="10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>89</v>
+      <c r="C11" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>13</v>
+        <v>85</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>14</v>
+      <c r="G12" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>88</v>
+        <v>99</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>15</v>
+        <v>109</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>93</v>
+        <v>11</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>99</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>99</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>7</v>
+        <v>72</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>72</v>
+      <c r="F17" s="7" t="s">
+        <v>150</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>99</v>
+        <v>90</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>99</v>
+        <v>93</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G20" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G21" s="1" t="s">
+      <c r="F21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>91</v>
+        <v>76</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>127</v>
+        <v>75</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>151</v>
+        <v>40</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>99</v>
+        <v>99</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G25" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>99</v>
@@ -1544,65 +1541,65 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>8</v>
+        <v>72</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>81</v>
+        <v>70</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="G28" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>100</v>
+        <v>9</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>99</v>
@@ -1613,283 +1610,283 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="1" t="s">
+      <c r="E34" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>79</v>
-      </c>
       <c r="D35" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>121</v>
+        <v>70</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>70</v>
+        <v>100</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>117</v>
+        <v>13</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E38" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>99</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>116</v>
+        <v>8</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>79</v>
+        <v>55</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>98</v>
+      <c r="A41" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>107</v>
+        <v>99</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>99</v>
@@ -1898,99 +1895,99 @@
         <v>99</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>140</v>
+      <c r="D45" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>8</v>
+      <c r="D46" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>99</v>
@@ -1998,97 +1995,97 @@
       <c r="F46" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
-        <v>59</v>
+      <c r="G46" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>99</v>
+        <v>99</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>142</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="1" t="s">
         <v>99</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="B49" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>99</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>128</v>
+        <v>65</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>99</v>
@@ -2096,21 +2093,21 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C51" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>99</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E51" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="F51" s="7" t="s">
+      <c r="E51" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>99</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -2119,114 +2116,114 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B52" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>99</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>99</v>
+        <v>110</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>111</v>
+        <v>86</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G54" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G54" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D55" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>99</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G55" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>99</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>99</v>
@@ -2234,7 +2231,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>99</v>
@@ -2252,29 +2249,6 @@
         <v>99</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G58" s="1" t="s">
         <v>99</v>
       </c>
     </row>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A218DC-EC0C-4081-9784-8A4D8FC4DD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720392BC-6649-400D-86A5-6DDB436E10B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3540" yWindow="0" windowWidth="18600" windowHeight="6708" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timetable" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="157">
   <si>
     <t>Teacher</t>
   </si>
@@ -499,6 +499,9 @@
   </si>
   <si>
     <t>12TH ARTS D+F</t>
+  </si>
+  <si>
+    <t>BABITA</t>
   </si>
 </sst>
 </file>
@@ -586,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -626,6 +629,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -928,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
@@ -2252,6 +2256,29 @@
         <v>99</v>
       </c>
     </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-management-v2\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96dbc1fdb7cb27ef/Desktop/Substitute-management-v2/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720392BC-6649-400D-86A5-6DDB436E10B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -363,9 +363,6 @@
     <t>11TH ARTS F</t>
   </si>
   <si>
-    <t>11TH ARTS A(3,4)</t>
-  </si>
-  <si>
     <t>12TH SCI A(5,6)</t>
   </si>
   <si>
@@ -502,6 +499,9 @@
   </si>
   <si>
     <t>BABITA</t>
+  </si>
+  <si>
+    <t>11TH SCI A(3,4)</t>
   </si>
 </sst>
 </file>
@@ -589,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -629,7 +629,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1051,7 +1050,7 @@
         <v>109</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>97</v>
@@ -1278,7 +1277,7 @@
         <v>99</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>99</v>
@@ -1330,7 +1329,7 @@
         <v>71</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>94</v>
@@ -1367,7 +1366,7 @@
         <v>69</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>99</v>
@@ -1471,12 +1470,12 @@
         <v>100</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -1643,7 +1642,7 @@
         <v>82</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>71</v>
@@ -1701,7 +1700,7 @@
         <v>99</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -1721,10 +1720,10 @@
         <v>99</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -1744,10 +1743,10 @@
         <v>70</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -1767,7 +1766,7 @@
         <v>16</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>99</v>
@@ -1790,10 +1789,10 @@
         <v>99</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -1813,10 +1812,10 @@
         <v>99</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G38" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1899,16 +1898,16 @@
         <v>99</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1919,19 +1918,19 @@
         <v>99</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="E43" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="F43" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -1945,16 +1944,16 @@
         <v>99</v>
       </c>
       <c r="D44" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E44" s="12" t="s">
-        <v>140</v>
-      </c>
       <c r="F44" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2014,16 +2013,16 @@
         <v>99</v>
       </c>
       <c r="D47" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E47" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="F47" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2037,16 +2036,16 @@
         <v>99</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F48" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2060,13 +2059,13 @@
         <v>93</v>
       </c>
       <c r="D49" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E49" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="E49" s="12" t="s">
-        <v>154</v>
-      </c>
       <c r="F49" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>99</v>
@@ -2120,7 +2119,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>99</v>
@@ -2135,15 +2134,15 @@
         <v>99</v>
       </c>
       <c r="F52" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G52" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>86</v>
@@ -2166,7 +2165,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>83</v>
@@ -2189,7 +2188,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>84</v>
@@ -2257,8 +2256,8 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="15" t="s">
-        <v>156</v>
+      <c r="A58" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>99</v>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96dbc1fdb7cb27ef/Desktop/Substitute-management-v2/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BCCE087-842C-4B36-90B1-FCAE48023C25}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -426,9 +426,6 @@
     <t>10TH (SKT)</t>
   </si>
   <si>
-    <t>11TH ARTS B (CS)</t>
-  </si>
-  <si>
     <t>12  ARTS+COMM+SCI (CS)</t>
   </si>
   <si>
@@ -502,6 +499,9 @@
   </si>
   <si>
     <t>11TH SCI A(3,4)</t>
+  </si>
+  <si>
+    <t>11TH SCI C + ARTS B</t>
   </si>
 </sst>
 </file>
@@ -562,7 +562,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -585,11 +585,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -629,6 +642,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1024,10 +1040,10 @@
         <v>87</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>84</v>
@@ -1043,20 +1059,20 @@
       <c r="B5" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>72</v>
+      <c r="C5" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>109</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>99</v>
+      <c r="G5" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1066,8 +1082,8 @@
       <c r="B6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>14</v>
+      <c r="C6" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>83</v>
@@ -1078,8 +1094,8 @@
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>99</v>
+      <c r="G6" s="9" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1118,11 +1134,11 @@
       <c r="D8" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F8" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>82</v>
@@ -1136,10 +1152,10 @@
         <v>76</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>100</v>
@@ -1181,8 +1197,8 @@
       <c r="B11" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>100</v>
+      <c r="C11" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>91</v>
@@ -1193,8 +1209,8 @@
       <c r="F11" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>14</v>
+      <c r="G11" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1230,8 +1246,8 @@
       <c r="C13" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>15</v>
+      <c r="D13" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>73</v>
@@ -1239,8 +1255,8 @@
       <c r="F13" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>99</v>
+      <c r="G13" s="9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1270,10 +1286,10 @@
       <c r="A15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>99</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -1293,23 +1309,23 @@
       <c r="A16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>77</v>
+      <c r="B16" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>99</v>
+      <c r="G16" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1329,7 +1345,7 @@
         <v>71</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>94</v>
@@ -1366,7 +1382,7 @@
         <v>69</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>99</v>
@@ -1475,7 +1491,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -1549,11 +1565,11 @@
       <c r="B27" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>103</v>
@@ -1595,17 +1611,17 @@
       <c r="B29" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>16</v>
+      <c r="C29" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>99</v>
@@ -1622,7 +1638,7 @@
         <v>99</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>7</v>
@@ -1642,13 +1658,13 @@
         <v>82</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>71</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>99</v>
@@ -1664,8 +1680,8 @@
       <c r="B32" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>12</v>
+      <c r="C32" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>14</v>
@@ -1676,8 +1692,8 @@
       <c r="F32" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>99</v>
+      <c r="G32" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1687,14 +1703,14 @@
       <c r="B33" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>15</v>
+      <c r="C33" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>99</v>
+      <c r="E33" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>99</v>
@@ -1731,16 +1747,16 @@
         <v>50</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="8" t="s">
         <v>71</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>70</v>
+      <c r="E35" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>117</v>
@@ -1759,11 +1775,11 @@
       <c r="C36" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E36" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>16</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>116</v>
@@ -1779,14 +1795,14 @@
       <c r="B37" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>112</v>
@@ -1872,7 +1888,7 @@
         <v>99</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>96</v>
@@ -1883,8 +1899,8 @@
       <c r="F41" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>17</v>
+      <c r="G41" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1895,7 +1911,7 @@
         <v>99</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>128</v>
@@ -1906,8 +1922,8 @@
       <c r="F42" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>130</v>
+      <c r="G42" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1918,19 +1934,19 @@
         <v>99</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="E43" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="F43" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>135</v>
+      <c r="G43" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -1941,19 +1957,19 @@
         <v>99</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="D44" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="E44" s="12" t="s">
-        <v>139</v>
-      </c>
       <c r="F44" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2009,20 +2025,20 @@
       <c r="B47" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>99</v>
+      <c r="C47" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="D47" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="E47" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="F47" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>143</v>
+      <c r="G47" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2033,19 +2049,19 @@
         <v>99</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2059,10 +2075,10 @@
         <v>93</v>
       </c>
       <c r="D49" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E49" s="12" t="s">
         <v>152</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>153</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>127</v>
@@ -2134,7 +2150,7 @@
         <v>99</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>110</v>
@@ -2257,7 +2273,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>99</v>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96dbc1fdb7cb27ef/Desktop/Substitute-management-v2/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BCCE087-842C-4B36-90B1-FCAE48023C25}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D2BF94E-1F7E-44BF-ABD3-FCF40C8C52CA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-312" yWindow="12" windowWidth="12492" windowHeight="11424" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timetable" sheetId="1" r:id="rId1"/>
@@ -1428,13 +1428,13 @@
         <v>12</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>77</v>
+      <c r="E21" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>73</v>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96dbc1fdb7cb27ef/Desktop/Substitute-management-v2/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D2BF94E-1F7E-44BF-ABD3-FCF40C8C52CA}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{665BD34E-A8C5-46FC-A953-CD410197F7DF}"/>
   <bookViews>
-    <workbookView xWindow="-312" yWindow="12" windowWidth="12492" windowHeight="11424" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timetable" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="159">
   <si>
     <t>Teacher</t>
   </si>
@@ -502,6 +502,12 @@
   </si>
   <si>
     <t>11TH SCI C + ARTS B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9TH </t>
+  </si>
+  <si>
+    <t>9TH (SKT)</t>
   </si>
 </sst>
 </file>
@@ -1897,7 +1903,7 @@
         <v>108</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>99</v>
@@ -1920,7 +1926,7 @@
         <v>129</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>99</v>
+        <v>158</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>99</v>
